--- a/output/pdf_financials_xlsx/PPL.xlsx
+++ b/output/pdf_financials_xlsx/PPL.xlsx
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="N124" s="3" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.000589</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>-0.001</v>
+        <v>-0.000987</v>
       </c>
       <c r="P124" s="1" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.000589</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-0.001</v>
+        <v>-0.000987</v>
       </c>
       <c r="P125" s="1" t="inlineStr">
         <is>
@@ -44736,7 +44736,11 @@
           <t>Receipt of finance lease payments</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -48643,7 +48647,11 @@
           <t>Receipt of finance lease payments 9</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PPL.xlsx
+++ b/output/pdf_financials_xlsx/PPL.xlsx
@@ -1126,46 +1126,46 @@
         <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.143602</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.183854</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.00023</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.000166</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.00013</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.000142</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.000306</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.00037</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.000558</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.000578</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.00084</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.0009</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.000972</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.000932</v>
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
@@ -2147,13 +2147,13 @@
         <v>0.241876</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.029624</v>
+        <v>0.213478</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.006911</v>
+        <v>0.007141</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.000494</v>
+        <v>0.00066</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2166,16 +2166,16 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.000655</v>
+        <v>0.000961</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.001025</v>
+        <v>0.001395</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.001742</v>
+        <v>0.0023</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.001528</v>
+        <v>0.002106</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.001665</v>
+        <v>0.002565</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.003219</v>
+        <v>0.004191</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.002189</v>
+        <v>0.003121</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2277,13 +2277,13 @@
         <v>0.308767</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.099843</v>
+        <v>0.283697</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.007091</v>
+        <v>0.007321</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.000665</v>
+        <v>0.000831</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2296,16 +2296,16 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.0009479999999999999</v>
+        <v>0.001254</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.001407</v>
+        <v>0.001777</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.002159</v>
+        <v>0.002717</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.002035</v>
+        <v>0.002613</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.002388</v>
+        <v>0.003288</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.003902</v>
+        <v>0.004874</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.002189</v>
+        <v>0.003121</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2345,13 +2345,13 @@
         <v>25.05839196877105</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.957041854359954</v>
+        <v>16.92652367172817</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>206.9156696819375</v>
+        <v>213.6270790779107</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>13.28405912904515</v>
+        <v>16.60007990411506</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -2364,16 +2364,16 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>22.2274325908558</v>
+        <v>29.4021101992966</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>26.05555555555555</v>
+        <v>32.9074074074074</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>29.37015372058223</v>
+        <v>36.96095769283091</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>31.93659761456372</v>
+        <v>41.0075329566855</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>27.68053784629651</v>
+        <v>38.11290135620726</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>33.60606321591595</v>
+        <v>41.97743519076737</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>23.98904109589041</v>
+        <v>34.2027397260274</v>
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="N126" s="3" t="n">
-        <v>-0.001386</v>
+        <v>-0.001521</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>-0.001525</v>
+        <v>-0.001651</v>
       </c>
       <c r="P126" s="1" t="inlineStr">
         <is>
@@ -70137,7 +70137,11 @@
           <t>Net finance costs (Note 19)</t>
         </is>
       </c>
-      <c r="D618" t="inlineStr"/>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E618" t="inlineStr">
         <is>
           <t>-</t>
@@ -72203,7 +72207,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E640" t="inlineStr">
         <is>
           <t>-</t>
@@ -72951,7 +72959,11 @@
           <t>Net finance costs (Note 18)</t>
         </is>
       </c>
-      <c r="D648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E648" t="inlineStr">
         <is>
           <t>-</t>
@@ -74402,7 +74414,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr"/>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E663" t="inlineStr">
         <is>
           <t>-</t>
@@ -76797,7 +76813,11 @@
           <t>Net finance costs (Note 21)</t>
         </is>
       </c>
-      <c r="D688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E688" t="inlineStr">
         <is>
           <t>-</t>
@@ -78353,7 +78373,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D704" t="inlineStr"/>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E704" t="inlineStr">
         <is>
           <t>-</t>
@@ -79365,7 +79389,11 @@
           <t>Net finance costs (Note 19)</t>
         </is>
       </c>
-      <c r="D714" t="inlineStr"/>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E714" t="inlineStr">
         <is>
           <t>-</t>
@@ -81618,7 +81646,11 @@
           <t>Net finance costs 19</t>
         </is>
       </c>
-      <c r="D737" t="inlineStr"/>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E737" t="inlineStr">
         <is>
           <t>-</t>
@@ -85359,7 +85391,11 @@
           <t>Net finance costs 18</t>
         </is>
       </c>
-      <c r="D776" t="inlineStr"/>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E776" t="inlineStr">
         <is>
           <t>-</t>
@@ -88485,7 +88521,11 @@
           <t>Net finance costs 17</t>
         </is>
       </c>
-      <c r="D808" t="inlineStr"/>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E808" t="inlineStr">
         <is>
           <t>-</t>
@@ -89370,7 +89410,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D817" t="inlineStr"/>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E817" t="inlineStr">
         <is>
           <t>-</t>
@@ -90047,7 +90091,11 @@
           <t>Net finance costs 21</t>
         </is>
       </c>
-      <c r="D824" t="inlineStr"/>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E824" t="inlineStr">
         <is>
           <t>-</t>
@@ -91728,7 +91776,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D841" t="inlineStr"/>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E841" t="inlineStr">
         <is>
           <t>-</t>
@@ -92116,7 +92168,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D845" t="inlineStr"/>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E845" t="inlineStr">
         <is>
           <t>-</t>
@@ -93914,7 +93970,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D863" t="inlineStr"/>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E863" t="inlineStr">
         <is>
           <t>-</t>
